--- a/app/src/main/assets/Bukti_Timbang_Barang_BTB.xlsx
+++ b/app/src/main/assets/Bukti_Timbang_Barang_BTB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>SLIP BUKTI TIMBANG BARANG (BTB)</t>
   </si>
@@ -19,12 +19,21 @@
     <t>Hari / Tgl</t>
   </si>
   <si>
+    <t xml:space="preserve">13/08/2026			</t>
+  </si>
+  <si>
     <t>NAME CUSTOMER</t>
   </si>
   <si>
+    <t xml:space="preserve">MUHAMMAD </t>
+  </si>
+  <si>
     <t>TRADEMARKS</t>
   </si>
   <si>
+    <t>LISA</t>
+  </si>
+  <si>
     <t>DATA TIMBANGAN</t>
   </si>
   <si>
@@ -38,6 +47,12 @@
   </si>
   <si>
     <t>JENIS BARANG :</t>
+  </si>
+  <si>
+    <t>HASIL SCAN</t>
+  </si>
+  <si>
+    <t>PEMBULATAN</t>
   </si>
   <si>
     <t>TOTAL :</t>
@@ -53,7 +68,7 @@
   <fonts count="8">
     <font>
       <sz val="11.0"/>
-      <color/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -73,13 +88,13 @@
       <sz val="11.0"/>
       <name val="Calibri"/>
     </font>
+    <font/>
     <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
       <sz val="11.0"/>
       <name val="Calibri"/>
@@ -199,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -210,41 +225,44 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="4" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -554,7 +572,7 @@
     <col customWidth="1" min="2" max="2" width="7.57"/>
     <col customWidth="1" min="3" max="3" width="8.14"/>
     <col customWidth="1" min="4" max="4" width="7.57"/>
-    <col customWidth="1" min="5" max="11" width="8.71"/>
+    <col customWidth="1" min="5" max="8" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -574,167 +592,171 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="D3" s="4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="24.75" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" ht="21.0" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
+      <c r="A8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" ht="21.0" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" ht="21.0" customHeight="1">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="A10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7"/>
       <c r="E10" s="12"/>
     </row>
     <row r="11" ht="21.0" customHeight="1">
       <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="12"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" ht="21.0" customHeight="1">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" ht="21.0" customHeight="1">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="12"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" ht="21.0" customHeight="1">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" ht="21.0" customHeight="1">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="12"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" ht="21.0" customHeight="1">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="12"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" ht="21.0" customHeight="1">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="12"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" ht="21.0" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="12"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" ht="21.0" customHeight="1">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="12"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" ht="21.0" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" ht="21.0" customHeight="1">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="15"/>
-      <c r="D21" s="15" t="str">
-        <f t="shared" ref="D21:D23" si="1">IF(OR(B21="", C21=""), "", B21*C21)</f>
-        <v/>
-      </c>
-      <c r="E21" s="12"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="14"/>
     </row>
     <row r="22" ht="21.0" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E22" s="12"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" ht="21.0" customHeight="1">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="15"/>
-      <c r="D23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E23" s="12"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="14"/>
     </row>
     <row r="24" ht="24.75" customHeight="1">
-      <c r="A24" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="19" t="str">
-        <f>SUM(D8:D23)</f>
+      <c r="A24" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="20" t="str">
+        <f>SUM(C11:D23)</f>
         <v>0.00</v>
       </c>
     </row>
@@ -742,7 +764,7 @@
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -820,7 +842,29 @@
     <row r="100" ht="15.75" customHeight="1"/>
     <row r="101" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="39">
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="D3:G3"/>
@@ -828,10 +872,16 @@
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
